--- a/2026-04/①②一般会計・収支予算書(収入・支出).xlsx
+++ b/2026-04/①②一般会計・収支予算書(収入・支出).xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/951bde4d8205714a/◆駒寄◆/★会計★/②一般会計/2025-R8会計年度/予算ねた/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="789" documentId="8_{F7D07766-F7B2-4E0D-B9FD-C7B50BB2D42E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E48212F8-0F48-4E52-9497-3603A1242968}"/>
+  <xr:revisionPtr revIDLastSave="928" documentId="8_{F7D07766-F7B2-4E0D-B9FD-C7B50BB2D42E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76AA12FC-5A9B-4C28-A1C3-1A7FBF9C205D}"/>
   <bookViews>
-    <workbookView xWindow="555" yWindow="105" windowWidth="17205" windowHeight="15090" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1905" yWindow="750" windowWidth="17580" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="（収　入）" sheetId="1" r:id="rId1"/>
-    <sheet name="（支　出）" sheetId="2" r:id="rId2"/>
+    <sheet name="令和８年度 一般会計 収支予算（案）" sheetId="1" r:id="rId1"/>
+    <sheet name="（支出）の分" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'（支　出）'!$A$1:$H$39</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'（収　入）'!$A$1:$H$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'（支出）の分'!$A$1:$H$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'令和８年度 一般会計 収支予算（案）'!$A$1:$H$34</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="105">
   <si>
     <t>本年度予算額</t>
     <rPh sb="0" eb="1">
@@ -307,13 +307,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>▼本年度</t>
-    <rPh sb="1" eb="4">
-      <t>ホンネンド</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>▼前年度</t>
     <rPh sb="1" eb="4">
       <t>ゼンネンド</t>
@@ -341,35 +334,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>前年度からの繰越金</t>
-    <rPh sb="0" eb="3">
-      <t>ゼンネンド</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>クリコシ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>キン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 198世帯 × 3.600円（6月収納）</t>
-    <rPh sb="4" eb="6">
-      <t>セタイ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>エン</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ガツ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>シュウノウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t xml:space="preserve">  (3) その他</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -384,47 +348,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t xml:space="preserve">  懇親餅つき大会ご祝儀 1万円</t>
-    <rPh sb="2" eb="4">
-      <t>コンシン</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>モチ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>タイカイ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>シュウギ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>マンエン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>器材等購入費（25万円)の８割補助</t>
-    <rPh sb="0" eb="2">
-      <t>キザイ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>トウ</t>
-    </rPh>
-    <rPh sb="3" eb="6">
-      <t>コウニュウヒ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>マンエン</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ワリ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ホジョ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t xml:space="preserve">  広報よこすか配布手数料 52,440円</t>
     <rPh sb="20" eb="21">
       <t>エン</t>
@@ -432,58 +355,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>　公園清掃報償金 33,400円</t>
-    <rPh sb="1" eb="3">
-      <t>コウエン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>セイソウ</t>
-    </rPh>
-    <rPh sb="5" eb="8">
-      <t>ホウショウキン</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>エン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">  資源回収奨励金 97,000円</t>
-    <rPh sb="16" eb="17">
-      <t>エン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">  防災訓練補助金 ３0,000円/100名</t>
-    <rPh sb="16" eb="17">
-      <t>エン</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>※以下合計（1,000円未満切捨て)</t>
-    <rPh sb="1" eb="3">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ゴウケイ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>エン</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ミマン</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>キリス</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>（支　出）</t>
     <rPh sb="1" eb="2">
       <t>シ</t>
@@ -650,19 +521,6 @@
     <phoneticPr fontId="22"/>
   </si>
   <si>
-    <t xml:space="preserve">  （前年度実績　105,427円）</t>
-    <rPh sb="3" eb="6">
-      <t>ゼンネンド</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ジッセキ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>エン</t>
-    </rPh>
-    <phoneticPr fontId="22"/>
-  </si>
-  <si>
     <t>　（2)青少年育成活動費</t>
     <rPh sb="4" eb="7">
       <t>セイショウネン</t>
@@ -751,28 +609,6 @@
     <phoneticPr fontId="22"/>
   </si>
   <si>
-    <t>　敬老（75才以上）祝い品 14万円</t>
-    <rPh sb="1" eb="3">
-      <t>ケイロウ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>イジョウ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>イワ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ヒン</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>マンエン</t>
-    </rPh>
-    <phoneticPr fontId="22"/>
-  </si>
-  <si>
     <t>3．広報活動費</t>
     <rPh sb="2" eb="4">
       <t>コウホウ</t>
@@ -925,16 +761,6 @@
     <phoneticPr fontId="22"/>
   </si>
   <si>
-    <t>▼資源回収分</t>
-    <rPh sb="1" eb="5">
-      <t>シゲンカイシュウ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ブン</t>
-    </rPh>
-    <phoneticPr fontId="22"/>
-  </si>
-  <si>
     <t>7.　積立金</t>
     <rPh sb="3" eb="5">
       <t>ツミタテ</t>
@@ -1016,193 +842,6 @@
     <phoneticPr fontId="22"/>
   </si>
   <si>
-    <t>　掃除用具,飲み物（前々年度実績 59,546円）</t>
-    <rPh sb="1" eb="3">
-      <t>ソウジ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ヨウグ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ノ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>モノ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>マエマエ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ドシ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ド</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ジッセキ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>エン</t>
-    </rPh>
-    <phoneticPr fontId="22"/>
-  </si>
-  <si>
-    <t>　ゴミかごネット他（前々年度実績 4,800円）</t>
-    <rPh sb="8" eb="9">
-      <t>タ</t>
-    </rPh>
-    <phoneticPr fontId="22"/>
-  </si>
-  <si>
-    <t>　学区ｿﾌﾄﾎﾞｰﾙ大会 3万円</t>
-    <rPh sb="1" eb="3">
-      <t>ガック</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>タイカイ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>マン</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>エン</t>
-    </rPh>
-    <phoneticPr fontId="22"/>
-  </si>
-  <si>
-    <t xml:space="preserve">  懇親餅つき大会 10万円</t>
-    <rPh sb="12" eb="14">
-      <t>マンエン</t>
-    </rPh>
-    <phoneticPr fontId="22"/>
-  </si>
-  <si>
-    <t>+会館蛍光灯LED化工事補助金 0 円</t>
-    <rPh sb="1" eb="3">
-      <t>カイカン</t>
-    </rPh>
-    <rPh sb="3" eb="6">
-      <t>ケイコウトウ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>コウジ</t>
-    </rPh>
-    <rPh sb="12" eb="15">
-      <t>ホジョキン</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>エン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>※218世帯, 会長活動費を含む</t>
-    <rPh sb="4" eb="6">
-      <t>セタイ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>カイチョウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>カツドウ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>フク</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>（218世帯なら、784.8千円）</t>
-    <rPh sb="4" eb="6">
-      <t>セタイ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>センエン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 会館蛍光灯LED化 48万円</t>
-    <rPh sb="1" eb="3">
-      <t>カイカン</t>
-    </rPh>
-    <rPh sb="3" eb="6">
-      <t>ケイコウトウ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>マンエン</t>
-    </rPh>
-    <phoneticPr fontId="22"/>
-  </si>
-  <si>
-    <t>　A3複合機 5万円+その他</t>
-    <rPh sb="3" eb="6">
-      <t>フクゴウキ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>マン</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>エン</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>タ</t>
-    </rPh>
-    <phoneticPr fontId="22"/>
-  </si>
-  <si>
-    <t xml:space="preserve">  船越ファミリーフェスティバル 6万円</t>
-    <rPh sb="2" eb="4">
-      <t>フナコシ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>マンエン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">  桜まつり 4万円</t>
-    <rPh sb="2" eb="3">
-      <t>サクラ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>マンエン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">  船越ファミリーフェスティバル 7万円</t>
-    <rPh sb="2" eb="4">
-      <t>フナコシ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>マンエン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">  さくら祭り 5万円</t>
-    <rPh sb="5" eb="6">
-      <t>マツ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>マン</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>エン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>　夜警 5千円</t>
     <rPh sb="5" eb="7">
       <t>センエン</t>
@@ -1217,14 +856,361 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>　（R6年度実績 231,820円）</t>
+    <t xml:space="preserve">  船越ファミリーフェスティバル 5万円</t>
+    <rPh sb="2" eb="4">
+      <t>フナコシ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>マンエン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  桜まつり 3万円</t>
+    <rPh sb="2" eb="3">
+      <t>サクラ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>マンエン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  懇親餅つき大会/芋煮会 9万円</t>
+    <rPh sb="10" eb="12">
+      <t>イモニ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>マンエン</t>
+    </rPh>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  （前年度実績　64,209 円）</t>
+    <rPh sb="3" eb="6">
+      <t>ゼンネンド</t>
+    </rPh>
     <rPh sb="6" eb="8">
       <t>ジッセキ</t>
     </rPh>
-    <phoneticPr fontId="22"/>
-  </si>
-  <si>
-    <t>　祝金、香典等（R8.2.1現在 41,000円）</t>
+    <rPh sb="16" eb="17">
+      <t>エン</t>
+    </rPh>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  （前年度実績　107,264 円）</t>
+    <rPh sb="3" eb="6">
+      <t>ゼンネンド</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジッセキ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>エン</t>
+    </rPh>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>　敬老（75才以上）祝い品 10万円</t>
+    <rPh sb="1" eb="3">
+      <t>ケイロウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>イワ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ヒン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>マンエン</t>
+    </rPh>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>　掃除用具,飲み物等</t>
+    <rPh sb="6" eb="7">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>モノ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>トウ</t>
+    </rPh>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>　掃除用具,飲み物（前年度実績 46,297円）</t>
+    <rPh sb="1" eb="3">
+      <t>ソウジ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヨウグ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>　（前年度実績 6,226円）</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>　名刺、スペアキー作成等</t>
+    <rPh sb="1" eb="3">
+      <t>メイシ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>トウ</t>
+    </rPh>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>▼R7年度の実績</t>
+    <rPh sb="3" eb="5">
+      <t>ネンド</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジッセキ</t>
+    </rPh>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>前年度からの繰越金（確定値）</t>
+    <rPh sb="0" eb="3">
+      <t>ゼンネンド</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>クリコシ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>キン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>チ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>　公園清掃報償金 66,800円</t>
+    <rPh sb="1" eb="3">
+      <t>コウエン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>セイソウ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ホウショウキン</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>エン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  資源回収奨励金 8,0000円</t>
+    <rPh sb="16" eb="17">
+      <t>エン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>▼本年度予想</t>
+    <rPh sb="1" eb="4">
+      <t>ホンネンド</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヨソウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>▼R8単年度の収支予想</t>
+    <rPh sb="3" eb="6">
+      <t>タンネンド</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シュウシ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヨソウ</t>
+    </rPh>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 189世帯 × 3,600円</t>
+    <rPh sb="4" eb="6">
+      <t>セタイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>エン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>230世帯×500円+204千円 = 319千円</t>
+    <rPh sb="3" eb="5">
+      <t>セタイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>エン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>エン</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>エン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  船越ファミリーフェスティバル  8 万円</t>
+    <rPh sb="2" eb="4">
+      <t>フナコシ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>マンエン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  さくら祭り 6 万円</t>
+    <rPh sb="5" eb="6">
+      <t>マツ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>マン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>エン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>内訳</t>
+    <rPh sb="0" eb="2">
+      <t>ウチワケ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> 会館LED化 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">万円, 消防点検 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1.43</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>万円</t>
+    </r>
+    <rPh sb="1" eb="3">
+      <t>カイカン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>マンエン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ショウボウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>テンケン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>マンエン</t>
+    </rPh>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>　印刷・事務用品等</t>
+    <rPh sb="1" eb="3">
+      <t>インサツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジム</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヨウヒン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ナド</t>
+    </rPh>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>　ソフトボール大会 4万円</t>
+    <rPh sb="7" eb="9">
+      <t>タイカイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>マン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>エン</t>
+    </rPh>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>　（前年度実績 216,320円）</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>　祝金、香典等（前年度実績  12,000円）</t>
     <rPh sb="1" eb="2">
       <t>イワイ</t>
     </rPh>
@@ -1237,57 +1223,62 @@
     <rPh sb="6" eb="7">
       <t>トウ</t>
     </rPh>
-    <rPh sb="14" eb="16">
-      <t>ゲンザイ</t>
-    </rPh>
-    <phoneticPr fontId="22"/>
-  </si>
-  <si>
-    <t xml:space="preserve">  臨時的経費</t>
-    <rPh sb="2" eb="5">
-      <t>リンジテキ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ケイヒ</t>
-    </rPh>
-    <phoneticPr fontId="22"/>
-  </si>
-  <si>
-    <t>※R7度繰越金は未確定</t>
-    <rPh sb="3" eb="4">
-      <t>ド</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>クリコシ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>キン</t>
-    </rPh>
     <rPh sb="8" eb="11">
-      <t>ミカクテイ</t>
+      <t>ゼンネンド</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジッセキ</t>
+    </rPh>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>　（前年度実績 19,580円）</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>器材等購入費（12.5万円)の８割として</t>
+    <rPh sb="0" eb="2">
+      <t>キザイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>コウニュウヒ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>マンエン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ワリ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>R7年度補助金実績 325千円 (7/31)</t>
-    <rPh sb="4" eb="7">
-      <t>ホジョキン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ジッセキ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>センエン</t>
+    <t>会長活動費 12,000円</t>
+    <rPh sb="0" eb="2">
+      <t>カイチョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カツドウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>エン</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>　（R8.2.1現在 6,226円）</t>
-    <phoneticPr fontId="22"/>
-  </si>
-  <si>
-    <t>　（R8.2.1現在 12,470円）</t>
-    <phoneticPr fontId="22"/>
+    <t xml:space="preserve">  防災訓練補助金 30,000円/100名</t>
+    <rPh sb="16" eb="17">
+      <t>エン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
   </si>
 </sst>
 </file>
@@ -1513,7 +1504,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2054,7 +2045,7 @@
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="260">
+  <cellXfs count="252">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2096,16 +2087,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="5" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="5" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="5" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2326,14 +2313,413 @@
     <xf numFmtId="176" fontId="10" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="38" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="25" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2353,15 +2739,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2374,439 +2751,29 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="25" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="12" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3115,7 +3082,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
@@ -3127,261 +3094,260 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="183" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="161"/>
+      <c r="B1" s="183"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="168" t="s">
+      <c r="A2" s="193" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="168"/>
+      <c r="B2" s="193"/>
       <c r="C2" s="12" t="s">
         <v>21</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="168" t="s">
+      <c r="G2" s="193" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="168"/>
+      <c r="H2" s="193"/>
     </row>
     <row r="3" spans="1:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="108" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="169"/>
-      <c r="C3" s="53" t="s">
+      <c r="B3" s="108"/>
+      <c r="C3" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="54" t="s">
+      <c r="D3" s="52" t="s">
         <v>1</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="169" t="s">
+      <c r="F3" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="169"/>
-      <c r="H3" s="169"/>
+      <c r="G3" s="108"/>
+      <c r="H3" s="108"/>
     </row>
     <row r="4" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="115" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="115"/>
-      <c r="C4" s="29">
-        <f>198*3600</f>
-        <v>712800</v>
-      </c>
-      <c r="D4" s="29">
+      <c r="A4" s="188" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="188"/>
+      <c r="C4" s="27">
+        <f>189*3600</f>
+        <v>680400</v>
+      </c>
+      <c r="D4" s="27">
         <f>190*12*300</f>
         <v>684000</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="65">
         <f>C4-D4</f>
-        <v>28800</v>
-      </c>
-      <c r="F4" s="166" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="167"/>
-      <c r="H4" s="167"/>
+        <v>-3600</v>
+      </c>
+      <c r="F4" s="189" t="s">
+        <v>91</v>
+      </c>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
       <c r="J4">
         <f>(164+3+29)*3600+10000</f>
         <v>715600</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="162"/>
-      <c r="B5" s="162"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="52"/>
+      <c r="A5" s="191"/>
+      <c r="B5" s="191"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="50"/>
       <c r="E5" s="8"/>
-      <c r="F5" s="255" t="s">
-        <v>91</v>
-      </c>
-      <c r="G5" s="256"/>
-      <c r="H5" s="256"/>
+      <c r="F5" s="244"/>
+      <c r="G5" s="245"/>
+      <c r="H5" s="245"/>
     </row>
     <row r="6" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="133" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="133"/>
-      <c r="C6" s="56">
+      <c r="A6" s="192" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="192"/>
+      <c r="C6" s="54">
         <f>C7+C11+C13</f>
-        <v>771000</v>
-      </c>
-      <c r="D6" s="56">
+        <v>660240</v>
+      </c>
+      <c r="D6" s="54">
         <f>D7+D11+D13</f>
         <v>815000</v>
       </c>
-      <c r="E6" s="65">
+      <c r="E6" s="63">
         <f>C6-D6</f>
-        <v>-44000</v>
-      </c>
-      <c r="F6" s="163"/>
-      <c r="G6" s="164"/>
-      <c r="H6" s="164"/>
+        <v>-154760</v>
+      </c>
+      <c r="F6" s="184"/>
+      <c r="G6" s="185"/>
+      <c r="H6" s="185"/>
     </row>
     <row r="7" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="136" t="s">
+      <c r="A7" s="186" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="136"/>
-      <c r="C7" s="36">
-        <v>325000</v>
-      </c>
-      <c r="D7" s="37">
+      <c r="B7" s="186"/>
+      <c r="C7" s="34">
+        <f>(230*500)+204000+12000</f>
+        <v>331000</v>
+      </c>
+      <c r="D7" s="35">
         <v>319000</v>
       </c>
       <c r="E7" s="7">
         <f>C7-D7</f>
-        <v>6000</v>
-      </c>
-      <c r="F7" s="110" t="s">
-        <v>104</v>
-      </c>
-      <c r="G7" s="151"/>
-      <c r="H7" s="151"/>
+        <v>12000</v>
+      </c>
+      <c r="F7" s="203" t="s">
+        <v>92</v>
+      </c>
+      <c r="G7" s="230"/>
+      <c r="H7" s="230"/>
       <c r="I7" s="11"/>
     </row>
     <row r="8" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="160" t="s">
+      <c r="A8" s="187" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="160"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="49"/>
+      <c r="B8" s="187"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="47"/>
       <c r="E8" s="6"/>
-      <c r="F8" s="165" t="s">
-        <v>90</v>
-      </c>
-      <c r="G8" s="165"/>
-      <c r="H8" s="165"/>
+      <c r="F8" s="144" t="s">
+        <v>103</v>
+      </c>
+      <c r="G8" s="144"/>
+      <c r="H8" s="144"/>
     </row>
     <row r="9" spans="1:10" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="145" t="s">
+      <c r="A9" s="194" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="145"/>
-      <c r="C9" s="36">
+      <c r="B9" s="194"/>
+      <c r="C9" s="34">
         <v>0</v>
       </c>
-      <c r="D9" s="37">
+      <c r="D9" s="35">
         <v>0</v>
       </c>
       <c r="E9" s="7">
         <f>C9-D9</f>
         <v>0</v>
       </c>
-      <c r="F9" s="110" t="s">
+      <c r="F9" s="124" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="151"/>
-      <c r="H9" s="151"/>
+      <c r="G9" s="101"/>
+      <c r="H9" s="101"/>
     </row>
     <row r="10" spans="1:10" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="154" t="s">
+      <c r="A10" s="195" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="154"/>
-      <c r="C10" s="45"/>
-      <c r="D10" s="46"/>
+      <c r="B10" s="195"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="44"/>
       <c r="E10" s="6"/>
-      <c r="F10" s="130"/>
-      <c r="G10" s="130"/>
-      <c r="H10" s="130"/>
+      <c r="F10" s="131"/>
+      <c r="G10" s="131"/>
+      <c r="H10" s="131"/>
     </row>
     <row r="11" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="155" t="s">
+      <c r="A11" s="196" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="156"/>
-      <c r="C11" s="48">
-        <v>200000</v>
-      </c>
-      <c r="D11" s="47">
+      <c r="B11" s="197"/>
+      <c r="C11" s="46">
+        <v>100000</v>
+      </c>
+      <c r="D11" s="45">
         <v>250000</v>
       </c>
       <c r="E11" s="7">
         <f>C11-D11</f>
-        <v>-50000</v>
-      </c>
-      <c r="F11" s="152" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" s="153"/>
-      <c r="H11" s="153"/>
+        <v>-150000</v>
+      </c>
+      <c r="F11" s="250" t="s">
+        <v>102</v>
+      </c>
+      <c r="G11" s="251"/>
+      <c r="H11" s="251"/>
       <c r="I11" s="11"/>
     </row>
     <row r="12" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="160" t="s">
+      <c r="A12" s="187" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="154"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="41"/>
+      <c r="B12" s="195"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="39"/>
       <c r="E12" s="6"/>
-      <c r="F12" s="130"/>
-      <c r="G12" s="130"/>
-      <c r="H12" s="130"/>
-      <c r="I12" s="24" t="s">
+      <c r="F12" s="131"/>
+      <c r="G12" s="131"/>
+      <c r="H12" s="131"/>
+      <c r="I12" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="J12" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="J12" s="24" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="13" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="136" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="145"/>
-      <c r="C13" s="36">
-        <f>INT(I13/1000)*1000</f>
-        <v>246000</v>
-      </c>
-      <c r="D13" s="36">
+      <c r="A13" s="186" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="194"/>
+      <c r="C13" s="34">
+        <f>SUM(I14:I17)</f>
+        <v>229240</v>
+      </c>
+      <c r="D13" s="34">
         <v>246000</v>
       </c>
       <c r="E13" s="7">
         <f>C13-D13</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="157" t="s">
-        <v>40</v>
-      </c>
-      <c r="G13" s="158"/>
-      <c r="H13" s="159"/>
+        <v>-16760</v>
+      </c>
+      <c r="F13" s="198" t="s">
+        <v>95</v>
+      </c>
+      <c r="G13" s="199"/>
+      <c r="H13" s="200"/>
       <c r="I13" s="11">
-        <f>SUM(I14:I19)</f>
-        <v>246240</v>
+        <f>SUM(I14:I18)</f>
+        <v>229240</v>
       </c>
       <c r="J13" s="11">
         <f>SUM(J14:J17)</f>
-        <v>212440</v>
+        <v>198040</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="136" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="145"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
+      <c r="A14" s="186" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="194"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
       <c r="E14" s="9"/>
-      <c r="F14" s="116" t="s">
-        <v>36</v>
-      </c>
-      <c r="G14" s="117"/>
-      <c r="H14" s="118"/>
+      <c r="F14" s="201" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="202"/>
+      <c r="H14" s="203"/>
       <c r="I14" s="11">
         <f>52440</f>
         <v>52440</v>
@@ -3392,16 +3358,16 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="104"/>
-      <c r="B15" s="105"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
+      <c r="A15" s="235"/>
+      <c r="B15" s="236"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
       <c r="E15" s="9"/>
-      <c r="F15" s="59" t="s">
-        <v>37</v>
-      </c>
-      <c r="G15" s="58"/>
-      <c r="H15" s="23"/>
+      <c r="F15" s="57" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" s="56"/>
+      <c r="H15" s="21"/>
       <c r="I15" s="11">
         <v>66800</v>
       </c>
@@ -3410,34 +3376,35 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="106"/>
-      <c r="B16" s="107"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
+      <c r="A16" s="237"/>
+      <c r="B16" s="238"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
       <c r="E16" s="9"/>
-      <c r="F16" s="116" t="s">
-        <v>38</v>
-      </c>
-      <c r="G16" s="117"/>
-      <c r="H16" s="118"/>
+      <c r="F16" s="201" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" s="202"/>
+      <c r="H16" s="203"/>
       <c r="I16" s="11">
-        <v>97000</v>
+        <v>80000</v>
       </c>
       <c r="J16" s="11">
-        <v>93200</v>
+        <f>'（支出）の分'!I35</f>
+        <v>78800</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="106"/>
-      <c r="B17" s="107"/>
+      <c r="A17" s="237"/>
+      <c r="B17" s="238"/>
       <c r="C17" s="16"/>
       <c r="D17" s="16"/>
       <c r="E17" s="9"/>
-      <c r="F17" s="57" t="s">
-        <v>39</v>
-      </c>
-      <c r="G17" s="58"/>
-      <c r="H17" s="23"/>
+      <c r="F17" s="55" t="s">
+        <v>104</v>
+      </c>
+      <c r="G17" s="56"/>
+      <c r="H17" s="21"/>
       <c r="I17" s="11">
         <v>30000</v>
       </c>
@@ -3445,373 +3412,415 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="16"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="257" t="s">
-        <v>89</v>
-      </c>
-      <c r="G18" s="258"/>
-      <c r="H18" s="259"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22">
+    <row r="18" spans="1:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="233"/>
+      <c r="B18" s="234"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="58"/>
+      <c r="G18" s="59"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="102"/>
-      <c r="B19" s="103"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="61"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21">
+    <row r="19" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="188" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="188"/>
+      <c r="C19" s="27">
+        <v>140000</v>
+      </c>
+      <c r="D19" s="27">
+        <v>24000</v>
+      </c>
+      <c r="E19" s="65">
+        <f>C19-D19</f>
+        <v>116000</v>
+      </c>
+      <c r="F19" s="240" t="s">
+        <v>93</v>
+      </c>
+      <c r="G19" s="240"/>
+      <c r="H19" s="240"/>
+    </row>
+    <row r="20" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="208"/>
+      <c r="B20" s="209"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="230" t="s">
+        <v>94</v>
+      </c>
+      <c r="G20" s="230"/>
+      <c r="H20" s="230"/>
+    </row>
+    <row r="21" spans="1:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="231"/>
+      <c r="B21" s="232"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="222"/>
+      <c r="G21" s="222"/>
+      <c r="H21" s="222"/>
+    </row>
+    <row r="22" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="192" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="192"/>
+      <c r="C22" s="27">
+        <f>C23+C24+C25</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="115" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="115"/>
-      <c r="C20" s="29">
-        <v>130000</v>
-      </c>
-      <c r="D20" s="29">
-        <v>24000</v>
-      </c>
-      <c r="E20" s="67">
-        <f>C20-D20</f>
-        <v>106000</v>
-      </c>
-      <c r="F20" s="112" t="s">
-        <v>34</v>
-      </c>
-      <c r="G20" s="112"/>
-      <c r="H20" s="112"/>
-    </row>
-    <row r="21" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="121"/>
-      <c r="B21" s="122"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="119" t="s">
-        <v>96</v>
-      </c>
-      <c r="G21" s="119"/>
-      <c r="H21" s="119"/>
-    </row>
-    <row r="22" spans="1:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="131"/>
-      <c r="B22" s="132"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="120" t="s">
-        <v>97</v>
-      </c>
-      <c r="G22" s="120"/>
-      <c r="H22" s="120"/>
+      <c r="D22" s="27">
+        <f>D23+D24+D25</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="27">
+        <f>C22-D22</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="229"/>
+      <c r="G22" s="131"/>
+      <c r="H22" s="131"/>
     </row>
     <row r="23" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="133" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" s="133"/>
-      <c r="C23" s="29">
-        <f>C24+C25+C26</f>
+      <c r="A23" s="223" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="224"/>
+      <c r="C23" s="30">
         <v>0</v>
       </c>
-      <c r="D23" s="29">
-        <f>D24+D25+D26</f>
+      <c r="D23" s="30">
         <v>0</v>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="3">
         <f>C23-D23</f>
         <v>0</v>
       </c>
-      <c r="F23" s="129"/>
-      <c r="G23" s="130"/>
-      <c r="H23" s="130"/>
+      <c r="F23" s="225"/>
+      <c r="G23" s="225"/>
+      <c r="H23" s="226"/>
     </row>
     <row r="24" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="123" t="s">
-        <v>16</v>
-      </c>
-      <c r="B24" s="124"/>
-      <c r="C24" s="32">
+      <c r="A24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="31">
         <v>0</v>
       </c>
-      <c r="D24" s="32">
+      <c r="D24" s="31">
         <v>0</v>
       </c>
       <c r="E24" s="3">
         <f>C24-D24</f>
         <v>0</v>
       </c>
-      <c r="F24" s="125"/>
-      <c r="G24" s="125"/>
-      <c r="H24" s="126"/>
+      <c r="F24" s="241"/>
+      <c r="G24" s="241"/>
+      <c r="H24" s="242"/>
+      <c r="I24" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="25" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="33">
+      <c r="A25" s="186" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="186"/>
+      <c r="C25" s="26">
         <v>0</v>
       </c>
-      <c r="D25" s="33">
+      <c r="D25" s="26">
         <v>0</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E25" s="7">
         <f>C25-D25</f>
         <v>0</v>
       </c>
-      <c r="F25" s="113"/>
-      <c r="G25" s="113"/>
-      <c r="H25" s="114"/>
-      <c r="I25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="136" t="s">
-        <v>17</v>
-      </c>
-      <c r="B26" s="136"/>
-      <c r="C26" s="28">
+      <c r="F25" s="203"/>
+      <c r="G25" s="230"/>
+      <c r="H25" s="230"/>
+    </row>
+    <row r="26" spans="1:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="211"/>
+      <c r="B26" s="212"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="123"/>
+      <c r="G26" s="221"/>
+      <c r="H26" s="124"/>
+      <c r="I26" s="11"/>
+    </row>
+    <row r="27" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="188" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="188"/>
+      <c r="C27" s="27">
         <v>0</v>
       </c>
-      <c r="D26" s="28">
+      <c r="D27" s="27">
         <v>0</v>
       </c>
-      <c r="E26" s="7">
-        <f>C26-D26</f>
+      <c r="E27" s="27">
+        <f>C27-D27</f>
         <v>0</v>
       </c>
-      <c r="F26" s="118"/>
-      <c r="G26" s="119"/>
-      <c r="H26" s="119"/>
-    </row>
-    <row r="27" spans="1:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="134"/>
-      <c r="B27" s="135"/>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="108"/>
-      <c r="G27" s="109"/>
-      <c r="H27" s="110"/>
-      <c r="I27" s="11"/>
-    </row>
-    <row r="28" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="115" t="s">
-        <v>18</v>
-      </c>
-      <c r="B28" s="115"/>
-      <c r="C28" s="29">
-        <v>0</v>
-      </c>
-      <c r="D28" s="29">
-        <v>0</v>
-      </c>
-      <c r="E28" s="29">
-        <f>C28-D28</f>
-        <v>0</v>
-      </c>
-      <c r="F28" s="111"/>
-      <c r="G28" s="112"/>
-      <c r="H28" s="112"/>
-    </row>
-    <row r="29" spans="1:10" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="121"/>
-      <c r="B29" s="122"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="108"/>
-      <c r="G29" s="109"/>
-      <c r="H29" s="110"/>
+      <c r="F27" s="239"/>
+      <c r="G27" s="240"/>
+      <c r="H27" s="240"/>
+    </row>
+    <row r="28" spans="1:10" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="208"/>
+      <c r="B28" s="209"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="123"/>
+      <c r="G28" s="221"/>
+      <c r="H28" s="124"/>
+      <c r="I28" s="18"/>
+    </row>
+    <row r="29" spans="1:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="210" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="210"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="222"/>
+      <c r="G29" s="222"/>
+      <c r="H29" s="222"/>
       <c r="I29" s="19"/>
     </row>
-    <row r="30" spans="1:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="150" t="s">
+    <row r="30" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="227" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" s="228"/>
+      <c r="C30" s="27">
+        <v>447358</v>
+      </c>
+      <c r="D30" s="27">
+        <v>713196</v>
+      </c>
+      <c r="E30" s="53">
+        <f>C30-D30</f>
+        <v>-265838</v>
+      </c>
+      <c r="F30" s="221" t="s">
+        <v>86</v>
+      </c>
+      <c r="G30" s="221"/>
+      <c r="H30" s="124"/>
+      <c r="J30" s="14"/>
+    </row>
+    <row r="31" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="211"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="217"/>
+      <c r="G31" s="218"/>
+      <c r="H31" s="219"/>
+    </row>
+    <row r="32" spans="1:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="194" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="150"/>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="120"/>
-      <c r="G30" s="120"/>
-      <c r="H30" s="120"/>
-      <c r="I30" s="20"/>
-    </row>
-    <row r="31" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="127" t="s">
-        <v>5</v>
-      </c>
-      <c r="B31" s="128"/>
-      <c r="C31" s="29">
-        <v>450000</v>
-      </c>
-      <c r="D31" s="29">
-        <v>713196</v>
-      </c>
-      <c r="E31" s="55">
-        <f>C31-D31</f>
-        <v>-263196</v>
-      </c>
-      <c r="F31" s="109" t="s">
-        <v>30</v>
-      </c>
-      <c r="G31" s="109"/>
-      <c r="H31" s="110"/>
-      <c r="J31" s="14"/>
-    </row>
-    <row r="32" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="134"/>
-      <c r="B32" s="135"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="142" t="s">
-        <v>103</v>
-      </c>
-      <c r="G32" s="143"/>
-      <c r="H32" s="144"/>
+      <c r="B32" s="194"/>
+      <c r="C32" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="E32" s="8"/>
+      <c r="F32" s="213"/>
+      <c r="G32" s="213"/>
+      <c r="H32" s="213"/>
     </row>
     <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="145" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33" s="145"/>
-      <c r="C33" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="D33" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="E33" s="8"/>
-      <c r="F33" s="138"/>
-      <c r="G33" s="138"/>
-      <c r="H33" s="138"/>
-    </row>
-    <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="146" t="s">
+      <c r="A33" s="204" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="147"/>
-      <c r="C34" s="29">
-        <f>C4+C6+C20+C23+C28+C31</f>
-        <v>2063800</v>
-      </c>
-      <c r="D34" s="44">
-        <f>D4+D6+D20+D23+D28+D31</f>
+      <c r="B33" s="205"/>
+      <c r="C33" s="27">
+        <f>C4+C6+C19+C22+C27+C30</f>
+        <v>1927998</v>
+      </c>
+      <c r="D33" s="42">
+        <f>D4+D6+D19+D22+D27+D30</f>
         <v>2236196</v>
       </c>
-      <c r="E34" s="66">
-        <f>C34-D34</f>
-        <v>-172396</v>
-      </c>
-      <c r="F34" s="139"/>
-      <c r="G34" s="140"/>
-      <c r="H34" s="140"/>
+      <c r="E33" s="64">
+        <f>C33-D33</f>
+        <v>-308198</v>
+      </c>
+      <c r="F33" s="214"/>
+      <c r="G33" s="215"/>
+      <c r="H33" s="215"/>
+    </row>
+    <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="207"/>
+      <c r="B34" s="207"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="38"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="216"/>
+      <c r="H34" s="216"/>
     </row>
     <row r="35" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="149"/>
-      <c r="B35" s="149"/>
-      <c r="C35" s="39"/>
-      <c r="D35" s="40"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="141"/>
-      <c r="G35" s="141"/>
-      <c r="H35" s="141"/>
+      <c r="A35" s="17"/>
+      <c r="B35" s="15"/>
     </row>
     <row r="36" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="18"/>
-      <c r="B36" s="15"/>
+      <c r="A36" s="206"/>
+      <c r="B36" s="206"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="202"/>
+      <c r="G36" s="202"/>
+      <c r="H36" s="202"/>
     </row>
     <row r="37" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="148"/>
-      <c r="B37" s="148"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="38"/>
+      <c r="A37" s="221"/>
+      <c r="B37" s="221"/>
+      <c r="C37" s="36"/>
+      <c r="D37" s="1"/>
       <c r="E37" s="1"/>
-      <c r="F37" s="117"/>
-      <c r="G37" s="117"/>
-      <c r="H37" s="117"/>
+      <c r="F37" s="202"/>
+      <c r="G37" s="202"/>
+      <c r="H37" s="202"/>
     </row>
     <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="109"/>
-      <c r="B38" s="109"/>
-      <c r="C38" s="38"/>
+      <c r="A38" s="221"/>
+      <c r="B38" s="221"/>
+      <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
-      <c r="F38" s="117"/>
-      <c r="G38" s="117"/>
-      <c r="H38" s="117"/>
+      <c r="F38" s="220"/>
+      <c r="G38" s="220"/>
+      <c r="H38" s="220"/>
     </row>
     <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="109"/>
-      <c r="B39" s="109"/>
+      <c r="A39" s="220"/>
+      <c r="B39" s="220"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
-      <c r="F39" s="137"/>
-      <c r="G39" s="137"/>
-      <c r="H39" s="137"/>
+      <c r="F39" s="220"/>
+      <c r="G39" s="220"/>
+      <c r="H39" s="220"/>
     </row>
     <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="137"/>
-      <c r="B40" s="137"/>
+      <c r="A40" s="220"/>
+      <c r="B40" s="220"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
-      <c r="F40" s="137"/>
-      <c r="G40" s="137"/>
-      <c r="H40" s="137"/>
+      <c r="F40" s="220"/>
+      <c r="G40" s="220"/>
+      <c r="H40" s="220"/>
     </row>
     <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="137"/>
-      <c r="B41" s="137"/>
+      <c r="A41" s="220"/>
+      <c r="B41" s="220"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
-      <c r="F41" s="137"/>
-      <c r="G41" s="137"/>
-      <c r="H41" s="137"/>
-    </row>
-    <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="137"/>
-      <c r="B42" s="137"/>
+      <c r="F41" s="220"/>
+      <c r="G41" s="220"/>
+      <c r="H41" s="220"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A42" s="220"/>
+      <c r="B42" s="220"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
-      <c r="F42" s="137"/>
-      <c r="G42" s="137"/>
-      <c r="H42" s="137"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A43" s="137"/>
-      <c r="B43" s="137"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="137"/>
-      <c r="G43" s="137"/>
-      <c r="H43" s="137"/>
+      <c r="F42" s="220"/>
+      <c r="G42" s="220"/>
+      <c r="H42" s="220"/>
     </row>
   </sheetData>
   <mergeCells count="77">
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="F5:H5"/>
     <mergeCell ref="F6:H6"/>
@@ -3827,75 +3836,13 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F21:H21"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.98425196850393704" right="0.39370078740157483" top="1.1811023622047245" bottom="0.78740157480314965" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
-    <oddHeader>&amp;C&amp;16令和８年度 一般会計 収支予算書（仮）&amp;R
-駒寄町内会</oddHeader>
+    <oddHeader>&amp;C&amp;16
+&amp;A&amp;R駒寄町内会</oddHeader>
   </headerFooter>
 </worksheet>
 </file>
@@ -3915,864 +3862,937 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="239" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1" s="239"/>
-      <c r="D1" s="69"/>
+      <c r="A1" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="105"/>
+      <c r="D1" s="67"/>
     </row>
     <row r="2" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="68"/>
+      <c r="A2" s="66"/>
       <c r="C2" s="13" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="G2" s="240" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" s="240"/>
-      <c r="I2" s="70" t="s">
-        <v>45</v>
+        <v>34</v>
+      </c>
+      <c r="G2" s="106" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="106"/>
+      <c r="I2" s="68" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="241" t="s">
+      <c r="A3" s="107" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="241"/>
-      <c r="C3" s="53" t="s">
+      <c r="B3" s="107"/>
+      <c r="C3" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="54" t="s">
+      <c r="D3" s="52" t="s">
         <v>1</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="169" t="s">
+      <c r="F3" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="169"/>
-      <c r="H3" s="169"/>
+      <c r="G3" s="108"/>
+      <c r="H3" s="108"/>
     </row>
     <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="242" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="242"/>
-      <c r="C4" s="71">
+      <c r="A4" s="109" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="109"/>
+      <c r="C4" s="69">
         <f>SUM(C5:C7)</f>
-        <v>730000</v>
-      </c>
-      <c r="D4" s="71">
+        <v>439300</v>
+      </c>
+      <c r="D4" s="69">
         <f>SUM(D5:D7)</f>
         <v>200000</v>
       </c>
-      <c r="E4" s="71">
+      <c r="E4" s="69">
         <f>C4-D4</f>
-        <v>530000</v>
-      </c>
-      <c r="F4" s="243"/>
-      <c r="G4" s="243"/>
-      <c r="H4" s="243"/>
+        <v>239300</v>
+      </c>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
     </row>
     <row r="5" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="234" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="234"/>
-      <c r="C5" s="72">
+      <c r="A5" s="247" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="247"/>
+      <c r="C5" s="248">
         <v>0</v>
       </c>
-      <c r="D5" s="72">
+      <c r="D5" s="248">
         <v>0</v>
       </c>
-      <c r="E5" s="73">
+      <c r="E5" s="249">
         <v>0</v>
       </c>
-      <c r="F5" s="234" t="s">
-        <v>48</v>
-      </c>
-      <c r="G5" s="234"/>
-      <c r="H5" s="234"/>
+      <c r="F5" s="247" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="247"/>
+      <c r="H5" s="247"/>
     </row>
     <row r="6" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="212" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="212"/>
-      <c r="C6" s="74">
-        <v>250000</v>
-      </c>
-      <c r="D6" s="74">
+      <c r="A6" s="111" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="111"/>
+      <c r="C6" s="72">
+        <v>125000</v>
+      </c>
+      <c r="D6" s="72">
         <v>200000</v>
       </c>
       <c r="E6" s="6">
         <f>C6-D6</f>
-        <v>50000</v>
-      </c>
-      <c r="F6" s="235" t="s">
+        <v>-75000</v>
+      </c>
+      <c r="F6" s="112" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="112"/>
+      <c r="H6" s="112"/>
+      <c r="I6" s="73">
+        <v>288750</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="113" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="113"/>
+      <c r="C7" s="74">
+        <v>314300</v>
+      </c>
+      <c r="D7" s="74">
+        <v>0</v>
+      </c>
+      <c r="E7" s="75">
+        <f>C7-D7</f>
+        <v>314300</v>
+      </c>
+      <c r="F7" s="146" t="s">
+        <v>96</v>
+      </c>
+      <c r="G7" s="147"/>
+      <c r="H7" s="148"/>
+      <c r="I7" s="73">
+        <v>276422</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="114" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="115"/>
+      <c r="C8" s="69">
+        <f>C9+C11+C13+C16+C18+C20</f>
+        <v>689000</v>
+      </c>
+      <c r="D8" s="69">
+        <f>D9+D11+D13+D16+D18+D20</f>
+        <v>735000</v>
+      </c>
+      <c r="E8" s="69">
+        <f>C8-D8</f>
+        <v>-46000</v>
+      </c>
+      <c r="F8" s="116" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="116"/>
+      <c r="H8" s="116"/>
+      <c r="I8" s="73">
+        <v>331688</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="117" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="117"/>
+      <c r="C9" s="70">
+        <v>60000</v>
+      </c>
+      <c r="D9" s="70">
+        <v>60000</v>
+      </c>
+      <c r="E9" s="76">
+        <f>C9-D9</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="113" t="s">
+        <v>97</v>
+      </c>
+      <c r="G9" s="113"/>
+      <c r="H9" s="113"/>
+      <c r="I9" s="73">
+        <v>73208</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="118"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="78"/>
+      <c r="F10" s="120" t="s">
+        <v>78</v>
+      </c>
+      <c r="G10" s="121"/>
+      <c r="H10" s="122"/>
+    </row>
+    <row r="11" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="123" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="124"/>
+      <c r="C11" s="79">
+        <v>164000</v>
+      </c>
+      <c r="D11" s="79">
+        <v>200000</v>
+      </c>
+      <c r="E11" s="76">
+        <f>C11-D11</f>
+        <v>-36000</v>
+      </c>
+      <c r="F11" s="125" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="126"/>
+      <c r="H11" s="127"/>
+      <c r="I11" s="73">
+        <v>85231</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="101"/>
+      <c r="B12" s="123"/>
+      <c r="C12" s="79"/>
+      <c r="D12" s="79"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="120" t="s">
+        <v>79</v>
+      </c>
+      <c r="G12" s="121"/>
+      <c r="H12" s="122"/>
+    </row>
+    <row r="13" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="117" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="117"/>
+      <c r="C13" s="70">
+        <v>170000</v>
+      </c>
+      <c r="D13" s="70">
+        <v>160000</v>
+      </c>
+      <c r="E13" s="76">
+        <f>C13-D13</f>
+        <v>10000</v>
+      </c>
+      <c r="F13" s="128" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="129"/>
+      <c r="H13" s="130"/>
+      <c r="I13" s="73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="101"/>
+      <c r="B14" s="101"/>
+      <c r="C14" s="99"/>
+      <c r="D14" s="99"/>
+      <c r="E14" s="100"/>
+      <c r="F14" s="102" t="s">
+        <v>75</v>
+      </c>
+      <c r="G14" s="103"/>
+      <c r="H14" s="104"/>
+    </row>
+    <row r="15" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="131"/>
+      <c r="B15" s="131"/>
+      <c r="C15" s="80"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="78"/>
+      <c r="F15" s="132" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" s="133"/>
+      <c r="H15" s="134"/>
+    </row>
+    <row r="16" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="123" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="124"/>
+      <c r="C16" s="79">
+        <v>140000</v>
+      </c>
+      <c r="D16" s="79">
+        <v>130000</v>
+      </c>
+      <c r="E16" s="76">
+        <f>C16-D16</f>
+        <v>10000</v>
+      </c>
+      <c r="F16" s="135" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16" s="135"/>
+      <c r="H16" s="135"/>
+      <c r="I16" s="73">
+        <v>5643</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="131"/>
+      <c r="B17" s="131"/>
+      <c r="C17" s="77"/>
+      <c r="D17" s="77"/>
+      <c r="E17" s="78"/>
+      <c r="F17" s="136" t="s">
         <v>50</v>
       </c>
-      <c r="G6" s="235"/>
-      <c r="H6" s="235"/>
-      <c r="I6" s="75">
-        <v>288750</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="209" t="s">
+      <c r="G17" s="137"/>
+      <c r="H17" s="138"/>
+    </row>
+    <row r="18" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="123" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="209"/>
-      <c r="C7" s="76">
-        <v>480000</v>
-      </c>
-      <c r="D7" s="76">
-        <v>0</v>
-      </c>
-      <c r="E7" s="77">
-        <f>C7-D7</f>
-        <v>480000</v>
-      </c>
-      <c r="F7" s="236" t="s">
-        <v>92</v>
-      </c>
-      <c r="G7" s="237"/>
-      <c r="H7" s="238"/>
-      <c r="I7" s="75">
-        <v>276422</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="203" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="197"/>
-      <c r="C8" s="71">
-        <f>C9+C11+C13+C16+C18+C20</f>
-        <v>725000</v>
-      </c>
-      <c r="D8" s="71">
-        <f>D10+D9+D11+D13+D16+D18+D20</f>
-        <v>735000</v>
-      </c>
-      <c r="E8" s="71">
-        <f>C8-D8</f>
-        <v>-10000</v>
-      </c>
-      <c r="F8" s="210" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8" s="210"/>
-      <c r="H8" s="210"/>
-      <c r="I8" s="75">
-        <v>331688</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="218" t="s">
-        <v>54</v>
-      </c>
-      <c r="B9" s="218"/>
-      <c r="C9" s="72">
-        <v>90000</v>
-      </c>
-      <c r="D9" s="72">
-        <v>60000</v>
-      </c>
-      <c r="E9" s="78">
-        <f>C9-D9</f>
-        <v>30000</v>
-      </c>
-      <c r="F9" s="209" t="s">
-        <v>93</v>
-      </c>
-      <c r="G9" s="209"/>
-      <c r="H9" s="209"/>
-      <c r="I9" s="75">
-        <v>73208</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="232"/>
-      <c r="B10" s="233"/>
-      <c r="C10" s="79"/>
-      <c r="D10" s="79"/>
-      <c r="E10" s="80"/>
-      <c r="F10" s="220" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10" s="221"/>
-      <c r="H10" s="222"/>
-    </row>
-    <row r="11" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="108" t="s">
-        <v>56</v>
-      </c>
-      <c r="B11" s="110"/>
-      <c r="C11" s="81">
-        <v>150000</v>
-      </c>
-      <c r="D11" s="81">
-        <v>200000</v>
-      </c>
-      <c r="E11" s="78">
-        <f>C11-D11</f>
-        <v>-50000</v>
-      </c>
-      <c r="F11" s="226" t="s">
-        <v>57</v>
-      </c>
-      <c r="G11" s="227"/>
-      <c r="H11" s="228"/>
-      <c r="I11" s="75">
-        <v>85231</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="151"/>
-      <c r="B12" s="108"/>
-      <c r="C12" s="81"/>
-      <c r="D12" s="81"/>
-      <c r="E12" s="80"/>
-      <c r="F12" s="229"/>
-      <c r="G12" s="230"/>
-      <c r="H12" s="231"/>
-    </row>
-    <row r="13" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="218" t="s">
-        <v>58</v>
-      </c>
-      <c r="B13" s="218"/>
-      <c r="C13" s="72">
-        <v>160000</v>
-      </c>
-      <c r="D13" s="72">
-        <v>160000</v>
-      </c>
-      <c r="E13" s="78">
-        <f>C13-D13</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="246" t="s">
-        <v>88</v>
-      </c>
-      <c r="G13" s="247"/>
-      <c r="H13" s="248"/>
-      <c r="I13" s="75">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="151"/>
-      <c r="B14" s="151"/>
-      <c r="C14" s="244"/>
-      <c r="D14" s="244"/>
-      <c r="E14" s="245"/>
-      <c r="F14" s="249" t="s">
-        <v>94</v>
-      </c>
-      <c r="G14" s="250"/>
-      <c r="H14" s="251"/>
-    </row>
-    <row r="15" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="130"/>
-      <c r="B15" s="130"/>
-      <c r="C15" s="82"/>
-      <c r="D15" s="82"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="252" t="s">
-        <v>95</v>
-      </c>
-      <c r="G15" s="253"/>
-      <c r="H15" s="254"/>
-    </row>
-    <row r="16" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="108" t="s">
-        <v>59</v>
-      </c>
-      <c r="B16" s="110"/>
-      <c r="C16" s="81">
-        <v>130000</v>
-      </c>
-      <c r="D16" s="81">
-        <v>130000</v>
-      </c>
-      <c r="E16" s="78">
-        <f>C16-D16</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="202" t="s">
-        <v>87</v>
-      </c>
-      <c r="G16" s="202"/>
-      <c r="H16" s="202"/>
-      <c r="I16" s="75">
-        <v>5643</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="130"/>
-      <c r="B17" s="130"/>
-      <c r="C17" s="79"/>
-      <c r="D17" s="79"/>
-      <c r="E17" s="80"/>
-      <c r="F17" s="223" t="s">
-        <v>60</v>
-      </c>
-      <c r="G17" s="224"/>
-      <c r="H17" s="225"/>
-    </row>
-    <row r="18" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="108" t="s">
-        <v>61</v>
-      </c>
-      <c r="B18" s="110"/>
-      <c r="C18" s="81">
+      <c r="B18" s="124"/>
+      <c r="C18" s="79">
         <v>35000</v>
       </c>
-      <c r="D18" s="81">
+      <c r="D18" s="79">
         <v>25000</v>
       </c>
-      <c r="E18" s="78">
+      <c r="E18" s="76">
         <f>C18-D18</f>
         <v>10000</v>
       </c>
-      <c r="F18" s="213" t="s">
-        <v>98</v>
-      </c>
-      <c r="G18" s="214"/>
-      <c r="H18" s="215"/>
+      <c r="F18" s="139" t="s">
+        <v>73</v>
+      </c>
+      <c r="G18" s="140"/>
+      <c r="H18" s="141"/>
       <c r="I18" s="14">
         <f>SUM(J18:J19)</f>
         <v>35293</v>
       </c>
-      <c r="J18" s="83">
+      <c r="J18" s="81">
         <v>3797</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="216"/>
-      <c r="B19" s="217"/>
-      <c r="C19" s="84"/>
-      <c r="D19" s="84"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="165" t="s">
-        <v>99</v>
-      </c>
-      <c r="G19" s="165"/>
-      <c r="H19" s="165"/>
-      <c r="I19" s="75"/>
-      <c r="J19" s="83">
+      <c r="A19" s="142"/>
+      <c r="B19" s="143"/>
+      <c r="C19" s="82"/>
+      <c r="D19" s="82"/>
+      <c r="E19" s="78"/>
+      <c r="F19" s="144" t="s">
+        <v>74</v>
+      </c>
+      <c r="G19" s="144"/>
+      <c r="H19" s="144"/>
+      <c r="I19" s="73"/>
+      <c r="J19" s="81">
         <v>31496</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="218" t="s">
-        <v>62</v>
-      </c>
-      <c r="B20" s="219"/>
-      <c r="C20" s="72">
+      <c r="A20" s="117" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="145"/>
+      <c r="C20" s="70">
+        <v>120000</v>
+      </c>
+      <c r="D20" s="70">
         <v>160000</v>
       </c>
-      <c r="D20" s="72">
-        <v>160000</v>
-      </c>
-      <c r="E20" s="78">
+      <c r="E20" s="76">
         <f>C20-D20</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="202" t="s">
-        <v>63</v>
-      </c>
-      <c r="G20" s="202"/>
-      <c r="H20" s="202"/>
-      <c r="I20" s="75">
+        <v>-40000</v>
+      </c>
+      <c r="F20" s="135" t="s">
+        <v>80</v>
+      </c>
+      <c r="G20" s="135"/>
+      <c r="H20" s="135"/>
+      <c r="I20" s="73">
         <v>118759</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="151"/>
-      <c r="B21" s="108"/>
-      <c r="C21" s="81"/>
-      <c r="D21" s="81"/>
-      <c r="E21" s="80"/>
-      <c r="F21" s="209" t="s">
-        <v>84</v>
-      </c>
-      <c r="G21" s="209"/>
-      <c r="H21" s="209"/>
-      <c r="I21" s="75">
+      <c r="A21" s="101"/>
+      <c r="B21" s="123"/>
+      <c r="C21" s="79"/>
+      <c r="D21" s="79"/>
+      <c r="E21" s="78"/>
+      <c r="F21" s="113" t="s">
+        <v>72</v>
+      </c>
+      <c r="G21" s="113"/>
+      <c r="H21" s="113"/>
+      <c r="I21" s="73">
         <v>13554</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="203" t="s">
-        <v>64</v>
-      </c>
-      <c r="B22" s="203"/>
-      <c r="C22" s="71">
+      <c r="A22" s="114" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="114"/>
+      <c r="C22" s="69">
         <f>C23+C24</f>
         <v>0</v>
       </c>
-      <c r="D22" s="71">
+      <c r="D22" s="69">
         <f>D23+D24</f>
         <v>0</v>
       </c>
-      <c r="E22" s="71">
+      <c r="E22" s="69">
         <v>0</v>
       </c>
-      <c r="F22" s="210"/>
-      <c r="G22" s="210"/>
-      <c r="H22" s="210"/>
+      <c r="F22" s="116"/>
+      <c r="G22" s="116"/>
+      <c r="H22" s="116"/>
     </row>
     <row r="23" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="211" t="s">
-        <v>65</v>
-      </c>
-      <c r="B23" s="211"/>
-      <c r="C23" s="85">
+      <c r="A23" s="149" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="149"/>
+      <c r="C23" s="83">
         <v>0</v>
       </c>
-      <c r="D23" s="85">
+      <c r="D23" s="83">
         <v>0</v>
       </c>
-      <c r="E23" s="73">
+      <c r="E23" s="71">
         <v>0</v>
       </c>
-      <c r="F23" s="212"/>
-      <c r="G23" s="212"/>
-      <c r="H23" s="212"/>
+      <c r="F23" s="111"/>
+      <c r="G23" s="111"/>
+      <c r="H23" s="111"/>
     </row>
     <row r="24" spans="1:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="151" t="s">
-        <v>66</v>
-      </c>
-      <c r="B24" s="151"/>
-      <c r="C24" s="81">
+      <c r="A24" s="101" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="101"/>
+      <c r="C24" s="79">
         <v>0</v>
       </c>
-      <c r="D24" s="81">
+      <c r="D24" s="79">
         <v>0</v>
       </c>
-      <c r="E24" s="86">
+      <c r="E24" s="84">
         <v>0</v>
       </c>
-      <c r="F24" s="202"/>
-      <c r="G24" s="202"/>
-      <c r="H24" s="202"/>
+      <c r="F24" s="135"/>
+      <c r="G24" s="135"/>
+      <c r="H24" s="135"/>
     </row>
     <row r="25" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="203" t="s">
-        <v>67</v>
-      </c>
-      <c r="B25" s="203"/>
-      <c r="C25" s="71">
+      <c r="A25" s="114" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="114"/>
+      <c r="C25" s="69">
         <f>C26+C27</f>
-        <v>65000</v>
-      </c>
-      <c r="D25" s="71">
+        <v>71800</v>
+      </c>
+      <c r="D25" s="69">
         <f>D26+D27</f>
         <v>70000</v>
       </c>
-      <c r="E25" s="71">
+      <c r="E25" s="69">
         <f>C25-D25</f>
-        <v>-5000</v>
-      </c>
-      <c r="F25" s="204"/>
-      <c r="G25" s="205"/>
-      <c r="H25" s="205"/>
+        <v>1800</v>
+      </c>
+      <c r="F25" s="150"/>
+      <c r="G25" s="151"/>
+      <c r="H25" s="151"/>
     </row>
     <row r="26" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="87" t="s">
-        <v>68</v>
-      </c>
-      <c r="B26" s="88"/>
-      <c r="C26" s="85">
+      <c r="A26" s="85" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="86"/>
+      <c r="C26" s="83">
+        <v>66800</v>
+      </c>
+      <c r="D26" s="83">
         <v>60000</v>
       </c>
-      <c r="D26" s="85">
-        <v>60000</v>
-      </c>
-      <c r="E26" s="89">
+      <c r="E26" s="87">
         <f>C26-D26</f>
-        <v>0</v>
-      </c>
-      <c r="F26" s="189" t="s">
-        <v>85</v>
-      </c>
-      <c r="G26" s="190"/>
-      <c r="H26" s="191"/>
-      <c r="I26" s="75">
+        <v>6800</v>
+      </c>
+      <c r="F26" s="152" t="s">
+        <v>82</v>
+      </c>
+      <c r="G26" s="153"/>
+      <c r="H26" s="154"/>
+      <c r="I26" s="73">
         <v>60073</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="90" t="s">
-        <v>69</v>
-      </c>
-      <c r="B27" s="91"/>
-      <c r="C27" s="92">
+      <c r="A27" s="88" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="89"/>
+      <c r="C27" s="90">
         <v>5000</v>
       </c>
-      <c r="D27" s="92">
+      <c r="D27" s="90">
         <v>10000</v>
       </c>
-      <c r="E27" s="93">
+      <c r="E27" s="91">
         <f>C27-D27</f>
         <v>-5000</v>
       </c>
-      <c r="F27" s="206" t="s">
-        <v>86</v>
-      </c>
-      <c r="G27" s="207"/>
-      <c r="H27" s="208"/>
-      <c r="I27" s="75">
+      <c r="F27" s="146" t="s">
+        <v>81</v>
+      </c>
+      <c r="G27" s="147"/>
+      <c r="H27" s="148"/>
+      <c r="I27" s="73">
         <v>6646</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="197" t="s">
-        <v>70</v>
-      </c>
-      <c r="B28" s="198"/>
-      <c r="C28" s="71">
+      <c r="A28" s="115" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" s="155"/>
+      <c r="C28" s="69">
         <f>C29+C30+C31+C32+C33</f>
-        <v>332000</v>
-      </c>
-      <c r="D28" s="71">
+        <v>382820</v>
+      </c>
+      <c r="D28" s="69">
         <f>D29+D30+D31+D32+D33</f>
         <v>371000</v>
       </c>
-      <c r="E28" s="71">
-        <f t="shared" ref="E28:E33" si="0">C28-D28</f>
-        <v>-39000</v>
-      </c>
-      <c r="F28" s="199"/>
-      <c r="G28" s="200"/>
-      <c r="H28" s="201"/>
-      <c r="I28" s="94"/>
+      <c r="E28" s="69">
+        <f>C28-D28</f>
+        <v>11820</v>
+      </c>
+      <c r="F28" s="156"/>
+      <c r="G28" s="157"/>
+      <c r="H28" s="158"/>
+      <c r="I28" s="92"/>
     </row>
     <row r="29" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="187" t="s">
-        <v>71</v>
-      </c>
-      <c r="B29" s="188"/>
-      <c r="C29" s="85">
-        <v>7000</v>
-      </c>
-      <c r="D29" s="85">
+      <c r="A29" s="159" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" s="160"/>
+      <c r="C29" s="83">
         <v>6000</v>
       </c>
-      <c r="E29" s="89">
+      <c r="D29" s="83">
+        <v>6000</v>
+      </c>
+      <c r="E29" s="87">
+        <f t="shared" ref="E28:E33" si="0">C29-D29</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="152" t="s">
+        <v>83</v>
+      </c>
+      <c r="G29" s="153"/>
+      <c r="H29" s="154"/>
+      <c r="I29" s="73">
+        <v>5001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="159" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="160"/>
+      <c r="C30" s="83">
+        <v>18000</v>
+      </c>
+      <c r="D30" s="83">
+        <v>15000</v>
+      </c>
+      <c r="E30" s="87">
         <f t="shared" si="0"/>
-        <v>1000</v>
-      </c>
-      <c r="F29" s="189" t="s">
-        <v>105</v>
-      </c>
-      <c r="G29" s="190"/>
-      <c r="H29" s="191"/>
-      <c r="I29" s="75">
-        <v>5001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="187" t="s">
-        <v>72</v>
-      </c>
-      <c r="B30" s="188"/>
-      <c r="C30" s="85">
-        <v>15000</v>
-      </c>
-      <c r="D30" s="85">
-        <v>15000</v>
-      </c>
-      <c r="E30" s="89">
+        <v>3000</v>
+      </c>
+      <c r="F30" s="152" t="s">
+        <v>101</v>
+      </c>
+      <c r="G30" s="153"/>
+      <c r="H30" s="154"/>
+      <c r="I30" s="73">
+        <v>4636</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="159" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="160"/>
+      <c r="C31" s="83">
+        <v>216320</v>
+      </c>
+      <c r="D31" s="83">
+        <v>207000</v>
+      </c>
+      <c r="E31" s="87">
+        <f>C31-D31</f>
+        <v>9320</v>
+      </c>
+      <c r="F31" s="152" t="s">
+        <v>99</v>
+      </c>
+      <c r="G31" s="153"/>
+      <c r="H31" s="154"/>
+      <c r="I31" s="73">
+        <v>187500</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="159" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="160"/>
+      <c r="C32" s="83">
+        <v>120000</v>
+      </c>
+      <c r="D32" s="83">
+        <v>120000</v>
+      </c>
+      <c r="E32" s="87">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F30" s="189" t="s">
-        <v>106</v>
-      </c>
-      <c r="G30" s="190"/>
-      <c r="H30" s="191"/>
-      <c r="I30" s="75">
-        <v>4636</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="187" t="s">
-        <v>73</v>
-      </c>
-      <c r="B31" s="188"/>
-      <c r="C31" s="85">
-        <v>232000</v>
-      </c>
-      <c r="D31" s="85">
-        <v>207000</v>
-      </c>
-      <c r="E31" s="89">
+      <c r="F32" s="152" t="s">
+        <v>100</v>
+      </c>
+      <c r="G32" s="153"/>
+      <c r="H32" s="154"/>
+      <c r="I32" s="73">
+        <v>75500</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="61" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" s="62"/>
+      <c r="C33" s="79">
+        <v>22500</v>
+      </c>
+      <c r="D33" s="79">
+        <v>23000</v>
+      </c>
+      <c r="E33" s="91">
         <f t="shared" si="0"/>
+        <v>-500</v>
+      </c>
+      <c r="F33" s="93" t="s">
+        <v>65</v>
+      </c>
+      <c r="G33" s="94"/>
+      <c r="H33" s="95"/>
+      <c r="I33" s="73">
+        <v>22520</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="161" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" s="162"/>
+      <c r="C34" s="96">
         <v>25000</v>
       </c>
-      <c r="F31" s="189" t="s">
-        <v>100</v>
-      </c>
-      <c r="G31" s="190"/>
-      <c r="H31" s="191"/>
-      <c r="I31" s="75">
-        <v>187500</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="187" t="s">
-        <v>74</v>
-      </c>
-      <c r="B32" s="188"/>
-      <c r="C32" s="85">
-        <v>55000</v>
-      </c>
-      <c r="D32" s="85">
-        <v>120000</v>
-      </c>
-      <c r="E32" s="89">
-        <f t="shared" si="0"/>
-        <v>-65000</v>
-      </c>
-      <c r="F32" s="189" t="s">
-        <v>101</v>
-      </c>
-      <c r="G32" s="190"/>
-      <c r="H32" s="191"/>
-      <c r="I32" s="75">
-        <v>75500</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="63" t="s">
-        <v>75</v>
-      </c>
-      <c r="B33" s="64"/>
-      <c r="C33" s="81">
-        <v>23000</v>
-      </c>
-      <c r="D33" s="81">
-        <v>23000</v>
-      </c>
-      <c r="E33" s="93">
-        <f t="shared" si="0"/>
+      <c r="D34" s="96">
+        <v>50000</v>
+      </c>
+      <c r="E34" s="69">
+        <f>C34-D34</f>
+        <v>-25000</v>
+      </c>
+      <c r="F34" s="163" t="s">
+        <v>84</v>
+      </c>
+      <c r="G34" s="164"/>
+      <c r="H34" s="165"/>
+      <c r="I34" s="243" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="166" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35" s="167"/>
+      <c r="C35" s="97">
         <v>0</v>
       </c>
-      <c r="F33" s="95" t="s">
-        <v>76</v>
-      </c>
-      <c r="G33" s="96"/>
-      <c r="H33" s="97"/>
-      <c r="I33" s="75">
-        <v>22520</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="192" t="s">
-        <v>77</v>
-      </c>
-      <c r="B34" s="193"/>
-      <c r="C34" s="98">
-        <v>30000</v>
-      </c>
-      <c r="D34" s="98">
-        <v>50000</v>
-      </c>
-      <c r="E34" s="71">
-        <f>C34-D34</f>
-        <v>-20000</v>
-      </c>
-      <c r="F34" s="194" t="s">
-        <v>102</v>
-      </c>
-      <c r="G34" s="195"/>
-      <c r="H34" s="196"/>
-      <c r="I34" s="99" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="178" t="s">
-        <v>79</v>
-      </c>
-      <c r="B35" s="179"/>
-      <c r="C35" s="100">
-        <v>0</v>
-      </c>
-      <c r="D35" s="100">
+      <c r="D35" s="97">
         <v>80000</v>
       </c>
-      <c r="E35" s="71">
+      <c r="E35" s="69">
         <f>C35-D35</f>
         <v>-80000</v>
       </c>
-      <c r="F35" s="180" t="s">
-        <v>80</v>
-      </c>
-      <c r="G35" s="181"/>
-      <c r="H35" s="182"/>
-      <c r="I35" s="75">
-        <v>97100</v>
+      <c r="F35" s="168" t="s">
+        <v>68</v>
+      </c>
+      <c r="G35" s="169"/>
+      <c r="H35" s="170"/>
+      <c r="I35" s="73">
+        <v>78800</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="165"/>
-      <c r="B36" s="165"/>
-      <c r="C36" s="82"/>
-      <c r="D36" s="82"/>
-      <c r="E36" s="101"/>
-      <c r="F36" s="183"/>
-      <c r="G36" s="184"/>
-      <c r="H36" s="185"/>
+      <c r="A36" s="144"/>
+      <c r="B36" s="144"/>
+      <c r="C36" s="80"/>
+      <c r="D36" s="80"/>
+      <c r="E36" s="98"/>
+      <c r="F36" s="171"/>
+      <c r="G36" s="172"/>
+      <c r="H36" s="173"/>
     </row>
     <row r="37" spans="1:9" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="186" t="s">
-        <v>81</v>
-      </c>
-      <c r="B37" s="186"/>
-      <c r="C37" s="71">
+      <c r="A37" s="174" t="s">
+        <v>69</v>
+      </c>
+      <c r="B37" s="174"/>
+      <c r="C37" s="69">
         <f>C38-C4-C8-C22-C25-C28-C34-C35</f>
-        <v>181800</v>
-      </c>
-      <c r="D37" s="71">
+        <v>320078</v>
+      </c>
+      <c r="D37" s="69">
         <f>D38-D4-D8-D22-D25-D28-D34-D35</f>
         <v>730196</v>
       </c>
-      <c r="E37" s="71">
+      <c r="E37" s="69">
         <f>C37-D37</f>
-        <v>-548396</v>
-      </c>
-      <c r="F37" s="174"/>
-      <c r="G37" s="174"/>
-      <c r="H37" s="174"/>
-      <c r="I37" s="75">
-        <v>2584603</v>
+        <v>-410118</v>
+      </c>
+      <c r="F37" s="175"/>
+      <c r="G37" s="175"/>
+      <c r="H37" s="175"/>
+      <c r="I37" s="73">
+        <v>447358</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="172" t="s">
-        <v>82</v>
-      </c>
-      <c r="B38" s="173"/>
-      <c r="C38" s="98">
-        <f>'（収　入）'!C34</f>
-        <v>2063800</v>
-      </c>
-      <c r="D38" s="98">
+      <c r="A38" s="177" t="s">
+        <v>70</v>
+      </c>
+      <c r="B38" s="178"/>
+      <c r="C38" s="96">
+        <f>'令和８年度 一般会計 収支予算（案）'!C33</f>
+        <v>1927998</v>
+      </c>
+      <c r="D38" s="96">
         <v>2236196</v>
       </c>
-      <c r="E38" s="98">
+      <c r="E38" s="96">
         <f>C38-D38</f>
-        <v>-172396</v>
-      </c>
-      <c r="F38" s="174"/>
-      <c r="G38" s="174"/>
-      <c r="H38" s="174"/>
-      <c r="I38" s="94" t="s">
-        <v>83</v>
+        <v>-308198</v>
+      </c>
+      <c r="F38" s="175"/>
+      <c r="G38" s="175"/>
+      <c r="H38" s="175"/>
+      <c r="I38" s="92" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="175"/>
-      <c r="B39" s="175"/>
+      <c r="A39" s="179"/>
+      <c r="B39" s="179"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
-      <c r="F39" s="176"/>
-      <c r="G39" s="176"/>
-      <c r="H39" s="176"/>
+      <c r="F39" s="180"/>
+      <c r="G39" s="180"/>
+      <c r="H39" s="180"/>
+      <c r="I39" s="243" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="40" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="177"/>
-      <c r="B40" s="170"/>
-      <c r="C40" s="170"/>
-      <c r="D40" s="170"/>
-      <c r="E40" s="170"/>
-      <c r="F40" s="170"/>
-      <c r="G40" s="170"/>
-      <c r="H40" s="170"/>
+      <c r="A40" s="181"/>
+      <c r="B40" s="176"/>
+      <c r="C40" s="176"/>
+      <c r="D40" s="176"/>
+      <c r="E40" s="176"/>
+      <c r="F40" s="176"/>
+      <c r="G40" s="176"/>
+      <c r="H40" s="176"/>
+      <c r="I40" s="246">
+        <f>C37-'令和８年度 一般会計 収支予算（案）'!C30</f>
+        <v>-127280</v>
+      </c>
     </row>
     <row r="41" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="170"/>
-      <c r="B41" s="170"/>
-      <c r="C41" s="170"/>
-      <c r="D41" s="170"/>
-      <c r="E41" s="170"/>
-      <c r="F41" s="170"/>
-      <c r="G41" s="170"/>
-      <c r="H41" s="170"/>
+      <c r="A41" s="176"/>
+      <c r="B41" s="176"/>
+      <c r="C41" s="176"/>
+      <c r="D41" s="176"/>
+      <c r="E41" s="176"/>
+      <c r="F41" s="176"/>
+      <c r="G41" s="176"/>
+      <c r="H41" s="176"/>
     </row>
     <row r="42" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="170"/>
-      <c r="B42" s="170"/>
-      <c r="C42" s="170"/>
-      <c r="D42" s="170"/>
-      <c r="E42" s="170"/>
-      <c r="F42" s="170"/>
-      <c r="G42" s="170"/>
-      <c r="H42" s="170"/>
+      <c r="A42" s="176"/>
+      <c r="B42" s="176"/>
+      <c r="C42" s="176"/>
+      <c r="D42" s="176"/>
+      <c r="E42" s="176"/>
+      <c r="F42" s="176"/>
+      <c r="G42" s="176"/>
+      <c r="H42" s="176"/>
     </row>
     <row r="43" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="170"/>
-      <c r="B43" s="170"/>
-      <c r="C43" s="170"/>
-      <c r="D43" s="170"/>
-      <c r="E43" s="170"/>
-      <c r="F43" s="170"/>
-      <c r="G43" s="170"/>
-      <c r="H43" s="170"/>
+      <c r="A43" s="176"/>
+      <c r="B43" s="176"/>
+      <c r="C43" s="176"/>
+      <c r="D43" s="176"/>
+      <c r="E43" s="176"/>
+      <c r="F43" s="176"/>
+      <c r="G43" s="176"/>
+      <c r="H43" s="176"/>
     </row>
     <row r="44" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="170"/>
-      <c r="B44" s="170"/>
-      <c r="C44" s="170"/>
-      <c r="D44" s="170"/>
-      <c r="E44" s="170"/>
-      <c r="F44" s="170"/>
-      <c r="G44" s="170"/>
-      <c r="H44" s="170"/>
+      <c r="A44" s="176"/>
+      <c r="B44" s="176"/>
+      <c r="C44" s="176"/>
+      <c r="D44" s="176"/>
+      <c r="E44" s="176"/>
+      <c r="F44" s="176"/>
+      <c r="G44" s="176"/>
+      <c r="H44" s="176"/>
     </row>
     <row r="45" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="170"/>
-      <c r="B45" s="170"/>
-      <c r="C45" s="170"/>
-      <c r="D45" s="170"/>
-      <c r="E45" s="170"/>
-      <c r="F45" s="170"/>
-      <c r="G45" s="170"/>
-      <c r="H45" s="170"/>
+      <c r="A45" s="176"/>
+      <c r="B45" s="176"/>
+      <c r="C45" s="176"/>
+      <c r="D45" s="176"/>
+      <c r="E45" s="176"/>
+      <c r="F45" s="176"/>
+      <c r="G45" s="176"/>
+      <c r="H45" s="176"/>
     </row>
     <row r="46" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="171"/>
-      <c r="B46" s="171"/>
-      <c r="C46" s="171"/>
-      <c r="D46" s="171"/>
-      <c r="E46" s="171"/>
-      <c r="F46" s="171"/>
-      <c r="G46" s="171"/>
-      <c r="H46" s="171"/>
+      <c r="A46" s="182"/>
+      <c r="B46" s="182"/>
+      <c r="C46" s="182"/>
+      <c r="D46" s="182"/>
+      <c r="E46" s="182"/>
+      <c r="F46" s="182"/>
+      <c r="G46" s="182"/>
+      <c r="H46" s="182"/>
     </row>
     <row r="47" spans="1:9" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A47" s="170"/>
-      <c r="B47" s="170"/>
-      <c r="C47" s="170"/>
-      <c r="D47" s="170"/>
-      <c r="E47" s="170"/>
-      <c r="F47" s="170"/>
-      <c r="G47" s="170"/>
-      <c r="H47" s="170"/>
+      <c r="A47" s="176"/>
+      <c r="B47" s="176"/>
+      <c r="C47" s="176"/>
+      <c r="D47" s="176"/>
+      <c r="E47" s="176"/>
+      <c r="F47" s="176"/>
+      <c r="G47" s="176"/>
+      <c r="H47" s="176"/>
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="F11:H11"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="A1:B1"/>
@@ -4789,76 +4809,12 @@
     <mergeCell ref="F7:H7"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="F8:H8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="A40:H40"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="A42:H42"/>
-    <mergeCell ref="A43:H43"/>
-    <mergeCell ref="A44:H44"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A46:H46"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.98425196850393704" right="0.39370078740157483" top="1.1811023622047245" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
-    <oddHeader>&amp;R&amp;D</oddHeader>
+    <oddHeader>&amp;R駒寄町内会</oddHeader>
   </headerFooter>
 </worksheet>
 </file>